--- a/output/upload/S00027_1986_기본형_급여_실손의료비보장보험_계약전환_단체개인전환_개인중지재개용_갱신형_무배당.xlsx
+++ b/output/upload/S00027_1986_기본형_급여_실손의료비보장보험_계약전환_단체개인전환_개인중지재개용_갱신형_무배당.xlsx
@@ -2628,29 +2628,29 @@
       </c>
       <c r="I7" s="6" t="inlineStr">
         <is>
-          <t>A999</t>
+          <t>N1</t>
         </is>
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>A999</t>
+          <t>N1</t>
         </is>
       </c>
       <c r="K7" s="6" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>N</t>
         </is>
       </c>
       <c r="L7" s="6" t="n">
-        <v>999</v>
+        <v>1</v>
       </c>
       <c r="M7" s="6" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N7" s="6" t="n">
-        <v>999</v>
+        <v>1</v>
       </c>
       <c r="O7" s="6" t="inlineStr">
         <is>

--- a/output/upload/S00027_1986_기본형_급여_실손의료비보장보험_계약전환_단체개인전환_개인중지재개용_갱신형_무배당.xlsx
+++ b/output/upload/S00027_1986_기본형_급여_실손의료비보장보험_계약전환_단체개인전환_개인중지재개용_갱신형_무배당.xlsx
@@ -2611,11 +2611,31 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n"/>
-      <c r="B7" s="5" t="inlineStr"/>
-      <c r="C7" s="5" t="n"/>
-      <c r="D7" s="5" t="inlineStr"/>
-      <c r="E7" s="5" t="n"/>
-      <c r="F7" s="5" t="n"/>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>1986001</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 기본형 급여 실손의료비보장보험[단체개인전환용](갱신형) 무배당(상해급여형)(100세형)</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>19861</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 기본형 급여 실손의료비보장보험[단체개인전환용](갱신형) 무배당(상해급여형)(100세형)</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
           <t>20260101</t>

--- a/output/upload/S00027_1986_기본형_급여_실손의료비보장보험_계약전환_단체개인전환_개인중지재개용_갱신형_무배당.xlsx
+++ b/output/upload/S00027_1986_기본형_급여_실손의료비보장보험_계약전환_단체개인전환_개인중지재개용_갱신형_무배당.xlsx
@@ -2623,7 +2623,7 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>19861</t>
+          <t>1986001</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">

--- a/output/upload/S00027_1986_기본형_급여_실손의료비보장보험_계약전환_단체개인전환_개인중지재개용_갱신형_무배당.xlsx
+++ b/output/upload/S00027_1986_기본형_급여_실손의료비보장보험_계약전환_단체개인전환_개인중지재개용_갱신형_무배당.xlsx
@@ -2714,20 +2714,72 @@
     </row>
     <row r="8">
       <c r="A8" s="5" t="n"/>
-      <c r="B8" s="5" t="n"/>
-      <c r="C8" s="5" t="n"/>
-      <c r="D8" s="5" t="n"/>
-      <c r="E8" s="5" t="n"/>
-      <c r="F8" s="5" t="n"/>
-      <c r="G8" s="6" t="n"/>
-      <c r="H8" s="6" t="n"/>
-      <c r="I8" s="6" t="n"/>
-      <c r="J8" s="6" t="n"/>
-      <c r="K8" s="6" t="n"/>
-      <c r="L8" s="6" t="n"/>
-      <c r="M8" s="6" t="n"/>
-      <c r="N8" s="6" t="n"/>
-      <c r="O8" s="6" t="n"/>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>1986002</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 기본형 급여 실손의료비보장보험[단체개인전환용](갱신형) 무배당(질병급여형)(100세형)</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>1986002</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 기본형 급여 실손의료비보장보험[단체개인전환용](갱신형) 무배당(질병급여형)(100세형)</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t>N1</t>
+        </is>
+      </c>
+      <c r="J8" s="6" t="inlineStr">
+        <is>
+          <t>N1</t>
+        </is>
+      </c>
+      <c r="K8" s="6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L8" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" s="6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N8" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="O8" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="P8" s="6" t="n"/>
       <c r="Q8" s="6" t="n"/>
       <c r="R8" s="6" t="n"/>

--- a/output/upload/S00027_1986_기본형_급여_실손의료비보장보험_계약전환_단체개인전환_개인중지재개용_갱신형_무배당.xlsx
+++ b/output/upload/S00027_1986_기본형_급여_실손의료비보장보험_계약전환_단체개인전환_개인중지재개용_갱신형_무배당.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="세트속성값" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="세트속성값" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
 </workbook>
